--- a/newdata.xlsx
+++ b/newdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Financials\financials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9404688-27D6-434C-9171-B3C5F196719A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE128B9-63D3-4471-B257-FBFA00CA8A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="16935" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="65">
   <si>
     <t>Date</t>
   </si>
@@ -224,6 +224,9 @@
   <si>
     <t>2081/82 Q1</t>
   </si>
+  <si>
+    <t>2081/82 Q2</t>
+  </si>
 </sst>
 </file>
 
@@ -371,7 +374,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -551,8 +554,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -667,6 +676,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -713,7 +759,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -739,6 +785,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="33" borderId="10" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="33" borderId="11" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="33" borderId="12" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1095,7 +1159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AL121"/>
+  <dimension ref="A1:AL141"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
@@ -15173,6 +15237,2349 @@
         <v>227.13</v>
       </c>
     </row>
+    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C122">
+        <v>207168154</v>
+      </c>
+      <c r="D122">
+        <v>320150123</v>
+      </c>
+      <c r="E122">
+        <v>251272784</v>
+      </c>
+      <c r="F122">
+        <v>251661862</v>
+      </c>
+      <c r="G122">
+        <v>20477020</v>
+      </c>
+      <c r="H122">
+        <v>19287936</v>
+      </c>
+      <c r="I122">
+        <v>35762241</v>
+      </c>
+      <c r="J122">
+        <v>10529484</v>
+      </c>
+      <c r="K122">
+        <v>7045604</v>
+      </c>
+      <c r="L122">
+        <v>3483880</v>
+      </c>
+      <c r="M122">
+        <v>617490.72</v>
+      </c>
+      <c r="N122">
+        <v>218664</v>
+      </c>
+      <c r="O122">
+        <v>548830</v>
+      </c>
+      <c r="P122">
+        <v>4868864</v>
+      </c>
+      <c r="Q122">
+        <v>857503</v>
+      </c>
+      <c r="R122">
+        <v>1885922.0120000001</v>
+      </c>
+      <c r="S122">
+        <v>149790.33333333334</v>
+      </c>
+      <c r="T122">
+        <v>1736131.6786666668</v>
+      </c>
+      <c r="U122">
+        <v>777674</v>
+      </c>
+      <c r="V122">
+        <v>2205267.9879999999</v>
+      </c>
+      <c r="W122">
+        <v>348</v>
+      </c>
+      <c r="X122">
+        <v>1347764.9879999999</v>
+      </c>
+      <c r="Y122">
+        <v>1348113</v>
+      </c>
+      <c r="Z122">
+        <v>390563</v>
+      </c>
+      <c r="AA122">
+        <v>957550</v>
+      </c>
+      <c r="AB122">
+        <v>1229875.345</v>
+      </c>
+      <c r="AC122">
+        <v>11.47</v>
+      </c>
+      <c r="AD122" s="11">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="AE122" s="11">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="AF122" s="11">
+        <v>4.3799999999999999E-2</v>
+      </c>
+      <c r="AG122" s="11">
+        <v>5.21E-2</v>
+      </c>
+      <c r="AH122" s="11">
+        <v>0.76129999999999998</v>
+      </c>
+      <c r="AI122" s="11">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="AJ122" s="11">
+        <v>3.8899999999999997E-2</v>
+      </c>
+      <c r="AK122" s="11">
+        <v>0.31630000000000003</v>
+      </c>
+      <c r="AL122" s="14">
+        <v>217.73</v>
+      </c>
+    </row>
+    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C123">
+        <v>162961835.69999999</v>
+      </c>
+      <c r="D123">
+        <v>227951804.03600001</v>
+      </c>
+      <c r="E123">
+        <v>193815478.537</v>
+      </c>
+      <c r="F123">
+        <v>197625110.19999999</v>
+      </c>
+      <c r="G123">
+        <v>5469439.0350000001</v>
+      </c>
+      <c r="H123">
+        <v>14769012.966</v>
+      </c>
+      <c r="I123">
+        <v>22211768.41</v>
+      </c>
+      <c r="J123">
+        <v>8889858.2599999998</v>
+      </c>
+      <c r="K123">
+        <v>5815286.5070000002</v>
+      </c>
+      <c r="L123">
+        <v>3074571.753</v>
+      </c>
+      <c r="M123">
+        <v>644712.10600000003</v>
+      </c>
+      <c r="N123">
+        <v>130038.201</v>
+      </c>
+      <c r="O123">
+        <v>85236.638000000006</v>
+      </c>
+      <c r="P123">
+        <v>3934558.6979999999</v>
+      </c>
+      <c r="Q123">
+        <v>1385354.6089999999</v>
+      </c>
+      <c r="R123">
+        <v>941355.60699999996</v>
+      </c>
+      <c r="S123">
+        <v>102434.71966666666</v>
+      </c>
+      <c r="T123">
+        <v>838920.88733333326</v>
+      </c>
+      <c r="U123">
+        <v>696477.09900000005</v>
+      </c>
+      <c r="V123">
+        <v>2296725.9920000001</v>
+      </c>
+      <c r="W123">
+        <v>10521.093999999999</v>
+      </c>
+      <c r="X123">
+        <v>911371.38300000015</v>
+      </c>
+      <c r="Y123">
+        <v>921912.47699999996</v>
+      </c>
+      <c r="Z123">
+        <v>260083.86300000001</v>
+      </c>
+      <c r="AA123">
+        <v>661828.61399999994</v>
+      </c>
+      <c r="AB123">
+        <v>158181.30100000001</v>
+      </c>
+      <c r="AC123">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="AD123" s="12">
+        <v>0.12870000000000001</v>
+      </c>
+      <c r="AE123" s="12">
+        <v>4.8500000000000001E-2</v>
+      </c>
+      <c r="AF123" s="12">
+        <v>5.2699999999999997E-2</v>
+      </c>
+      <c r="AG123" s="12">
+        <v>6.0499999999999998E-2</v>
+      </c>
+      <c r="AH123" s="12">
+        <v>0.84460000000000002</v>
+      </c>
+      <c r="AI123" s="12">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="AJ123" s="12">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="AK123" s="12">
+        <v>0.249</v>
+      </c>
+      <c r="AL123" s="15">
+        <v>150.38999999999999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C124">
+        <v>216659317</v>
+      </c>
+      <c r="D124">
+        <v>314869163</v>
+      </c>
+      <c r="E124">
+        <v>250430513</v>
+      </c>
+      <c r="F124">
+        <v>252590408</v>
+      </c>
+      <c r="G124">
+        <v>3603613</v>
+      </c>
+      <c r="H124">
+        <v>12944694</v>
+      </c>
+      <c r="I124">
+        <v>29227346</v>
+      </c>
+      <c r="J124">
+        <v>10300535</v>
+      </c>
+      <c r="K124">
+        <v>5984715</v>
+      </c>
+      <c r="L124">
+        <v>4315821</v>
+      </c>
+      <c r="M124">
+        <v>765040</v>
+      </c>
+      <c r="N124">
+        <v>213158</v>
+      </c>
+      <c r="O124">
+        <v>5378</v>
+      </c>
+      <c r="P124">
+        <v>5299397</v>
+      </c>
+      <c r="Q124">
+        <v>349598</v>
+      </c>
+      <c r="R124">
+        <v>1263963</v>
+      </c>
+      <c r="S124">
+        <v>345200.44444444444</v>
+      </c>
+      <c r="T124">
+        <v>918762.5555555555</v>
+      </c>
+      <c r="U124">
+        <v>578180</v>
+      </c>
+      <c r="V124">
+        <v>3457254</v>
+      </c>
+      <c r="W124">
+        <v>-853</v>
+      </c>
+      <c r="X124">
+        <v>3107656</v>
+      </c>
+      <c r="Y124">
+        <v>3106804</v>
+      </c>
+      <c r="Z124">
+        <v>1032041</v>
+      </c>
+      <c r="AA124">
+        <v>2074763</v>
+      </c>
+      <c r="AB124">
+        <v>2716771</v>
+      </c>
+      <c r="AC124">
+        <v>32.06</v>
+      </c>
+      <c r="AD124" s="12">
+        <v>0.1132</v>
+      </c>
+      <c r="AE124" s="12">
+        <v>6.6E-3</v>
+      </c>
+      <c r="AF124" s="12">
+        <v>4.24E-2</v>
+      </c>
+      <c r="AG124" s="12">
+        <v>0.14549999999999999</v>
+      </c>
+      <c r="AH124" s="12">
+        <v>0.85389999999999999</v>
+      </c>
+      <c r="AI124" s="12">
+        <v>5.6599999999999998E-2</v>
+      </c>
+      <c r="AJ124" s="12">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="AK124" s="12">
+        <v>0.29260000000000003</v>
+      </c>
+      <c r="AL124" s="15">
+        <v>225.79</v>
+      </c>
+    </row>
+    <row r="125" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C125">
+        <v>421035056</v>
+      </c>
+      <c r="D125">
+        <v>640248760</v>
+      </c>
+      <c r="E125">
+        <v>513982868</v>
+      </c>
+      <c r="F125">
+        <v>534072500</v>
+      </c>
+      <c r="G125">
+        <v>10685949</v>
+      </c>
+      <c r="H125">
+        <v>38115853</v>
+      </c>
+      <c r="I125">
+        <v>64638614</v>
+      </c>
+      <c r="J125">
+        <v>22682599</v>
+      </c>
+      <c r="K125">
+        <v>14384074</v>
+      </c>
+      <c r="L125">
+        <v>8298525</v>
+      </c>
+      <c r="M125">
+        <v>1600445</v>
+      </c>
+      <c r="N125">
+        <v>376622</v>
+      </c>
+      <c r="O125">
+        <v>108351</v>
+      </c>
+      <c r="P125">
+        <v>10383943</v>
+      </c>
+      <c r="Q125">
+        <v>2203748</v>
+      </c>
+      <c r="R125">
+        <v>2311798</v>
+      </c>
+      <c r="S125">
+        <v>467306.77777777775</v>
+      </c>
+      <c r="T125">
+        <v>1844491.2222222222</v>
+      </c>
+      <c r="U125">
+        <v>1664177</v>
+      </c>
+      <c r="V125">
+        <v>6407968</v>
+      </c>
+      <c r="W125">
+        <v>1542</v>
+      </c>
+      <c r="X125">
+        <v>4204220</v>
+      </c>
+      <c r="Y125">
+        <v>4205761</v>
+      </c>
+      <c r="Z125">
+        <v>1152272</v>
+      </c>
+      <c r="AA125">
+        <v>3053489</v>
+      </c>
+      <c r="AB125">
+        <v>2645342</v>
+      </c>
+      <c r="AC125">
+        <v>16.02</v>
+      </c>
+      <c r="AD125" s="12">
+        <v>0.12590000000000001</v>
+      </c>
+      <c r="AE125" s="12">
+        <v>4.8599999999999997E-2</v>
+      </c>
+      <c r="AF125" s="12">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="AG125" s="12">
+        <v>9.69E-2</v>
+      </c>
+      <c r="AH125" s="12">
+        <v>0.7853</v>
+      </c>
+      <c r="AI125" s="12">
+        <v>6.9500000000000006E-2</v>
+      </c>
+      <c r="AJ125" s="12">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="AK125" s="12">
+        <v>0.33460000000000001</v>
+      </c>
+      <c r="AL125" s="15">
+        <v>169.58</v>
+      </c>
+    </row>
+    <row r="126" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C126">
+        <v>240614012.69999999</v>
+      </c>
+      <c r="D126">
+        <v>366424634.02100003</v>
+      </c>
+      <c r="E126">
+        <v>298319934.60000002</v>
+      </c>
+      <c r="F126">
+        <v>304545247.10000002</v>
+      </c>
+      <c r="G126">
+        <v>8381015.3109999998</v>
+      </c>
+      <c r="H126">
+        <v>21656615.631999999</v>
+      </c>
+      <c r="I126">
+        <v>38139754.600000001</v>
+      </c>
+      <c r="J126">
+        <v>14642764.456</v>
+      </c>
+      <c r="K126">
+        <v>9407116.4600000009</v>
+      </c>
+      <c r="L126">
+        <v>5235647.9960000003</v>
+      </c>
+      <c r="M126">
+        <v>456979.41499999998</v>
+      </c>
+      <c r="N126">
+        <v>267240.93400000001</v>
+      </c>
+      <c r="O126">
+        <v>115723.25900000001</v>
+      </c>
+      <c r="P126">
+        <v>6075591.6040000003</v>
+      </c>
+      <c r="Q126">
+        <v>184600.94699999999</v>
+      </c>
+      <c r="R126">
+        <v>1818028.66</v>
+      </c>
+      <c r="S126">
+        <v>241287.85711111111</v>
+      </c>
+      <c r="T126">
+        <v>1576740.8028888889</v>
+      </c>
+      <c r="U126">
+        <v>949592.35900000005</v>
+      </c>
+      <c r="V126">
+        <v>3307970.585</v>
+      </c>
+      <c r="W126">
+        <v>-951778.924</v>
+      </c>
+      <c r="X126">
+        <v>3123369.6379999998</v>
+      </c>
+      <c r="Y126">
+        <v>2171590.7140000002</v>
+      </c>
+      <c r="Z126">
+        <v>652820.64399999997</v>
+      </c>
+      <c r="AA126">
+        <v>1518770.07</v>
+      </c>
+      <c r="AB126">
+        <v>-3950945.0449999999</v>
+      </c>
+      <c r="AC126">
+        <v>14.03</v>
+      </c>
+      <c r="AD126" s="12">
+        <v>0.1157</v>
+      </c>
+      <c r="AE126" s="12">
+        <v>4.9799999999999997E-2</v>
+      </c>
+      <c r="AF126" s="12">
+        <v>5.2200000000000003E-2</v>
+      </c>
+      <c r="AG126" s="12">
+        <v>8.1299999999999997E-2</v>
+      </c>
+      <c r="AH126" s="12">
+        <v>0.78369999999999995</v>
+      </c>
+      <c r="AI126" s="12">
+        <v>7.3029999999999998E-2</v>
+      </c>
+      <c r="AJ126" s="12">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="AK126" s="12">
+        <v>0.2702</v>
+      </c>
+      <c r="AL126" s="15">
+        <v>176.11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C127">
+        <v>288046944.15399998</v>
+      </c>
+      <c r="D127">
+        <v>436747675.412</v>
+      </c>
+      <c r="E127">
+        <v>348749107.85100001</v>
+      </c>
+      <c r="F127">
+        <v>367883521.60000002</v>
+      </c>
+      <c r="G127">
+        <v>13981755.33</v>
+      </c>
+      <c r="H127">
+        <v>26255861.34</v>
+      </c>
+      <c r="I127">
+        <v>35014714.630999997</v>
+      </c>
+      <c r="J127">
+        <v>16337070.404999999</v>
+      </c>
+      <c r="K127">
+        <v>11023106.093</v>
+      </c>
+      <c r="L127">
+        <v>5313964.3119999999</v>
+      </c>
+      <c r="M127">
+        <v>1270719.2450000001</v>
+      </c>
+      <c r="N127">
+        <v>148974.462</v>
+      </c>
+      <c r="O127">
+        <v>349959.17200000002</v>
+      </c>
+      <c r="P127">
+        <v>7083617.1900000004</v>
+      </c>
+      <c r="Q127">
+        <v>3273141.9130000002</v>
+      </c>
+      <c r="R127">
+        <v>2135103.37</v>
+      </c>
+      <c r="S127">
+        <v>76713.179000000004</v>
+      </c>
+      <c r="T127">
+        <v>2058390.1910000001</v>
+      </c>
+      <c r="U127">
+        <v>953810.81400000001</v>
+      </c>
+      <c r="V127">
+        <v>3994703.0060000001</v>
+      </c>
+      <c r="W127">
+        <v>-31142.481</v>
+      </c>
+      <c r="X127">
+        <v>721561.09299999988</v>
+      </c>
+      <c r="Y127">
+        <v>690418.61100000003</v>
+      </c>
+      <c r="Z127">
+        <v>414688.15299999999</v>
+      </c>
+      <c r="AA127">
+        <v>275730.45799999998</v>
+      </c>
+      <c r="AB127">
+        <v>-6477695.7549999999</v>
+      </c>
+      <c r="AC127">
+        <v>2.1</v>
+      </c>
+      <c r="AD127" s="12">
+        <v>0.1172</v>
+      </c>
+      <c r="AE127" s="12">
+        <v>6.9599999999999995E-2</v>
+      </c>
+      <c r="AF127" s="12">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="AG127" s="12">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="AH127" s="12">
+        <v>0.81840000000000002</v>
+      </c>
+      <c r="AI127" s="12">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="AJ127" s="12">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="AK127" s="12">
+        <v>0.30609999999999998</v>
+      </c>
+      <c r="AL127" s="15">
+        <v>133.51</v>
+      </c>
+    </row>
+    <row r="128" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C128">
+        <v>275555935</v>
+      </c>
+      <c r="D128">
+        <v>409975857</v>
+      </c>
+      <c r="E128">
+        <v>340499661</v>
+      </c>
+      <c r="F128">
+        <v>345198452</v>
+      </c>
+      <c r="G128">
+        <v>7000000</v>
+      </c>
+      <c r="H128">
+        <v>24346512</v>
+      </c>
+      <c r="I128">
+        <v>41997906</v>
+      </c>
+      <c r="J128">
+        <v>14718376</v>
+      </c>
+      <c r="K128">
+        <v>9528259</v>
+      </c>
+      <c r="L128">
+        <v>5190116</v>
+      </c>
+      <c r="M128">
+        <v>998973</v>
+      </c>
+      <c r="N128">
+        <v>175767</v>
+      </c>
+      <c r="O128">
+        <v>345814</v>
+      </c>
+      <c r="P128">
+        <v>6710671</v>
+      </c>
+      <c r="Q128">
+        <v>1929255</v>
+      </c>
+      <c r="R128">
+        <v>2061223</v>
+      </c>
+      <c r="S128">
+        <v>185508.55555555556</v>
+      </c>
+      <c r="T128">
+        <v>1875714.4444444445</v>
+      </c>
+      <c r="U128">
+        <v>927176</v>
+      </c>
+      <c r="V128">
+        <v>3722272</v>
+      </c>
+      <c r="W128">
+        <v>-123439</v>
+      </c>
+      <c r="X128">
+        <v>1793017</v>
+      </c>
+      <c r="Y128">
+        <v>1669577</v>
+      </c>
+      <c r="Z128">
+        <v>507501</v>
+      </c>
+      <c r="AA128">
+        <v>1162076</v>
+      </c>
+      <c r="AB128">
+        <v>368529</v>
+      </c>
+      <c r="AC128">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="AD128" s="12">
+        <v>0.12180000000000001</v>
+      </c>
+      <c r="AE128" s="12">
+        <v>5.67E-2</v>
+      </c>
+      <c r="AF128" s="12">
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="AG128" s="12">
+        <v>5.6300000000000003E-2</v>
+      </c>
+      <c r="AH128" s="12">
+        <v>0.79190000000000005</v>
+      </c>
+      <c r="AI128" s="12">
+        <v>7.17E-2</v>
+      </c>
+      <c r="AJ128" s="12">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="AK128" s="12">
+        <v>0.30109999999999998</v>
+      </c>
+      <c r="AL128" s="15">
+        <v>172.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C129">
+        <v>140006167</v>
+      </c>
+      <c r="D129">
+        <v>199953309</v>
+      </c>
+      <c r="E129">
+        <v>165484423</v>
+      </c>
+      <c r="F129">
+        <v>171119495</v>
+      </c>
+      <c r="G129">
+        <v>5494734</v>
+      </c>
+      <c r="H129">
+        <v>11621357</v>
+      </c>
+      <c r="I129">
+        <v>17919653</v>
+      </c>
+      <c r="J129">
+        <v>7429334</v>
+      </c>
+      <c r="K129">
+        <v>4605664</v>
+      </c>
+      <c r="L129">
+        <v>2823670</v>
+      </c>
+      <c r="M129">
+        <v>672104.84400000004</v>
+      </c>
+      <c r="N129">
+        <v>148401</v>
+      </c>
+      <c r="O129">
+        <v>55765</v>
+      </c>
+      <c r="P129">
+        <v>3699941</v>
+      </c>
+      <c r="Q129">
+        <v>204703</v>
+      </c>
+      <c r="R129">
+        <v>1264791.0020000001</v>
+      </c>
+      <c r="S129">
+        <v>128147.22222222222</v>
+      </c>
+      <c r="T129">
+        <v>1136643.7797777778</v>
+      </c>
+      <c r="U129">
+        <v>607650</v>
+      </c>
+      <c r="V129">
+        <v>1827499.9979999997</v>
+      </c>
+      <c r="W129">
+        <v>-469473</v>
+      </c>
+      <c r="X129">
+        <v>1622796.9979999997</v>
+      </c>
+      <c r="Y129">
+        <v>1153325</v>
+      </c>
+      <c r="Z129">
+        <v>345997</v>
+      </c>
+      <c r="AA129">
+        <v>807327</v>
+      </c>
+      <c r="AB129">
+        <v>166290.12299999999</v>
+      </c>
+      <c r="AC129">
+        <v>13.89</v>
+      </c>
+      <c r="AD129" s="12">
+        <v>0.1326</v>
+      </c>
+      <c r="AE129" s="12">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="AF129" s="12">
+        <v>4.82E-2</v>
+      </c>
+      <c r="AG129" s="12">
+        <v>9.2200000000000004E-2</v>
+      </c>
+      <c r="AH129" s="12">
+        <v>0.82720000000000005</v>
+      </c>
+      <c r="AI129" s="12">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="AJ129" s="12">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="AK129" s="12">
+        <v>0.27339999999999998</v>
+      </c>
+      <c r="AL129" s="15">
+        <v>154.19999999999999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C130">
+        <v>405172955</v>
+      </c>
+      <c r="D130">
+        <v>585480490</v>
+      </c>
+      <c r="E130">
+        <v>480240715</v>
+      </c>
+      <c r="F130">
+        <v>489164152</v>
+      </c>
+      <c r="G130">
+        <v>9626107</v>
+      </c>
+      <c r="H130">
+        <v>27056997</v>
+      </c>
+      <c r="I130">
+        <v>59256855</v>
+      </c>
+      <c r="J130">
+        <v>20419444</v>
+      </c>
+      <c r="K130">
+        <v>12523494</v>
+      </c>
+      <c r="L130">
+        <v>7895949</v>
+      </c>
+      <c r="M130">
+        <v>1511442</v>
+      </c>
+      <c r="N130">
+        <v>342636</v>
+      </c>
+      <c r="O130">
+        <v>319372</v>
+      </c>
+      <c r="P130">
+        <v>10069399</v>
+      </c>
+      <c r="Q130">
+        <v>1351009</v>
+      </c>
+      <c r="R130">
+        <v>2381900</v>
+      </c>
+      <c r="S130">
+        <v>515158</v>
+      </c>
+      <c r="T130">
+        <v>1866742</v>
+      </c>
+      <c r="U130">
+        <v>1159080</v>
+      </c>
+      <c r="V130">
+        <v>6528419</v>
+      </c>
+      <c r="W130">
+        <v>-540988</v>
+      </c>
+      <c r="X130">
+        <v>5177410</v>
+      </c>
+      <c r="Y130">
+        <v>4636422</v>
+      </c>
+      <c r="Z130">
+        <v>1392145</v>
+      </c>
+      <c r="AA130">
+        <v>3244277</v>
+      </c>
+      <c r="AB130">
+        <v>1891735</v>
+      </c>
+      <c r="AC130">
+        <v>24.05</v>
+      </c>
+      <c r="AD130" s="12">
+        <v>0.1178</v>
+      </c>
+      <c r="AE130" s="12">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="AF130" s="12">
+        <v>4.8099999999999997E-2</v>
+      </c>
+      <c r="AG130" s="12">
+        <v>0.1103</v>
+      </c>
+      <c r="AH130" s="12">
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="AI130" s="12">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="AJ130" s="12">
+        <v>3.7400000000000003E-2</v>
+      </c>
+      <c r="AK130" s="12">
+        <v>0.25940000000000002</v>
+      </c>
+      <c r="AL130" s="15">
+        <v>219.01</v>
+      </c>
+    </row>
+    <row r="131" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C131">
+        <v>216032215.80000001</v>
+      </c>
+      <c r="D131">
+        <v>364845496.30199999</v>
+      </c>
+      <c r="E131">
+        <v>305983479</v>
+      </c>
+      <c r="F131">
+        <v>307835709.5</v>
+      </c>
+      <c r="G131">
+        <v>3495258.6970000002</v>
+      </c>
+      <c r="H131">
+        <v>14694022.927999999</v>
+      </c>
+      <c r="I131">
+        <v>38491829.839000002</v>
+      </c>
+      <c r="J131">
+        <v>11445110.084000001</v>
+      </c>
+      <c r="K131">
+        <v>6818468.8820000002</v>
+      </c>
+      <c r="L131">
+        <v>4626641.2029999997</v>
+      </c>
+      <c r="M131">
+        <v>541311.10900000005</v>
+      </c>
+      <c r="N131">
+        <v>78254.505999999994</v>
+      </c>
+      <c r="O131">
+        <v>189246.14300000001</v>
+      </c>
+      <c r="P131">
+        <v>5435472.96</v>
+      </c>
+      <c r="Q131">
+        <v>2527442.0290000001</v>
+      </c>
+      <c r="R131">
+        <v>1843844.919</v>
+      </c>
+      <c r="S131">
+        <v>46497.020111111109</v>
+      </c>
+      <c r="T131">
+        <v>1797347.8988888888</v>
+      </c>
+      <c r="U131">
+        <v>647418.21400000004</v>
+      </c>
+      <c r="V131">
+        <v>2944209.827</v>
+      </c>
+      <c r="W131">
+        <v>1705.383</v>
+      </c>
+      <c r="X131">
+        <v>416767.79799999995</v>
+      </c>
+      <c r="Y131">
+        <v>418473.18099999998</v>
+      </c>
+      <c r="Z131">
+        <v>-42544.466</v>
+      </c>
+      <c r="AA131">
+        <v>461017.647</v>
+      </c>
+      <c r="AB131">
+        <v>607175.73899999994</v>
+      </c>
+      <c r="AC131">
+        <v>6.27</v>
+      </c>
+      <c r="AD131" s="12">
+        <v>0.1295</v>
+      </c>
+      <c r="AE131" s="12">
+        <v>4.99E-2</v>
+      </c>
+      <c r="AF131" s="12">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="AG131" s="12">
+        <v>2.4199999999999999E-2</v>
+      </c>
+      <c r="AH131" s="12">
+        <v>0.72399999999999998</v>
+      </c>
+      <c r="AI131" s="12">
+        <v>6.1600000000000002E-2</v>
+      </c>
+      <c r="AJ131" s="12">
+        <v>3.9100000000000003E-2</v>
+      </c>
+      <c r="AK131" s="12">
+        <v>0.3634</v>
+      </c>
+      <c r="AL131" s="15">
+        <v>261.95999999999998</v>
+      </c>
+    </row>
+    <row r="132" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C132">
+        <v>342017519</v>
+      </c>
+      <c r="D132">
+        <v>533186191</v>
+      </c>
+      <c r="E132">
+        <v>440879270</v>
+      </c>
+      <c r="F132">
+        <v>445145957</v>
+      </c>
+      <c r="G132">
+        <v>10040000</v>
+      </c>
+      <c r="H132">
+        <v>34128595</v>
+      </c>
+      <c r="I132">
+        <v>63155580</v>
+      </c>
+      <c r="J132">
+        <v>18684566</v>
+      </c>
+      <c r="K132">
+        <v>11319442</v>
+      </c>
+      <c r="L132">
+        <v>7365124</v>
+      </c>
+      <c r="M132">
+        <v>1005798</v>
+      </c>
+      <c r="N132">
+        <v>319680</v>
+      </c>
+      <c r="O132">
+        <v>321645</v>
+      </c>
+      <c r="P132">
+        <v>9012246</v>
+      </c>
+      <c r="Q132">
+        <v>1772593</v>
+      </c>
+      <c r="R132">
+        <v>1970459</v>
+      </c>
+      <c r="S132">
+        <v>449999.77777777775</v>
+      </c>
+      <c r="T132">
+        <v>1520459.2222222222</v>
+      </c>
+      <c r="U132">
+        <v>1225817</v>
+      </c>
+      <c r="V132">
+        <v>5815970</v>
+      </c>
+      <c r="W132">
+        <v>6620</v>
+      </c>
+      <c r="X132">
+        <v>4043377</v>
+      </c>
+      <c r="Y132">
+        <v>4049998</v>
+      </c>
+      <c r="Z132">
+        <v>1217672</v>
+      </c>
+      <c r="AA132">
+        <v>2832326</v>
+      </c>
+      <c r="AB132">
+        <v>-2863553</v>
+      </c>
+      <c r="AC132">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="AD132" s="12">
+        <v>0.1295</v>
+      </c>
+      <c r="AE132" s="12">
+        <v>5.8599999999999999E-2</v>
+      </c>
+      <c r="AF132" s="12">
+        <v>4.6300000000000001E-2</v>
+      </c>
+      <c r="AG132" s="12">
+        <v>9.1899999999999996E-2</v>
+      </c>
+      <c r="AH132" s="12">
+        <v>0.78869999999999996</v>
+      </c>
+      <c r="AI132" s="12">
+        <v>6.5799999999999997E-2</v>
+      </c>
+      <c r="AJ132" s="12">
+        <v>3.9600000000000003E-2</v>
+      </c>
+      <c r="AK132" s="12">
+        <v>0.33750000000000002</v>
+      </c>
+      <c r="AL132" s="15">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="133" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C133">
+        <v>139430075</v>
+      </c>
+      <c r="D133">
+        <v>222671098</v>
+      </c>
+      <c r="E133">
+        <v>189269303</v>
+      </c>
+      <c r="F133">
+        <v>192471715</v>
+      </c>
+      <c r="G133">
+        <v>5844388</v>
+      </c>
+      <c r="H133">
+        <v>10500152</v>
+      </c>
+      <c r="I133">
+        <v>19641135</v>
+      </c>
+      <c r="J133">
+        <v>7650694</v>
+      </c>
+      <c r="K133">
+        <v>5357327</v>
+      </c>
+      <c r="L133">
+        <v>2293367</v>
+      </c>
+      <c r="M133">
+        <v>563537.11100000003</v>
+      </c>
+      <c r="N133">
+        <v>111296</v>
+      </c>
+      <c r="O133">
+        <v>20383</v>
+      </c>
+      <c r="P133">
+        <v>2988584</v>
+      </c>
+      <c r="Q133">
+        <v>239228</v>
+      </c>
+      <c r="R133">
+        <v>886904.06900000002</v>
+      </c>
+      <c r="S133">
+        <v>149258.27333333332</v>
+      </c>
+      <c r="T133">
+        <v>737645.7956666667</v>
+      </c>
+      <c r="U133">
+        <v>524292</v>
+      </c>
+      <c r="V133">
+        <v>1577387.9309999999</v>
+      </c>
+      <c r="W133">
+        <v>5165</v>
+      </c>
+      <c r="X133">
+        <v>1338159.9309999999</v>
+      </c>
+      <c r="Y133">
+        <v>1343324.46</v>
+      </c>
+      <c r="Z133">
+        <v>443043</v>
+      </c>
+      <c r="AA133">
+        <v>900281</v>
+      </c>
+      <c r="AB133">
+        <v>1207098.088</v>
+      </c>
+      <c r="AC133">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="AD133" s="12">
+        <v>0.12870000000000001</v>
+      </c>
+      <c r="AE133" s="12">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="AF133" s="12">
+        <v>5.5800000000000002E-2</v>
+      </c>
+      <c r="AG133" s="12">
+        <v>9.2100000000000001E-2</v>
+      </c>
+      <c r="AH133" s="12">
+        <v>0.72819999999999996</v>
+      </c>
+      <c r="AI133" s="12">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="AJ133" s="12">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="AK133" s="12">
+        <v>0.36570000000000003</v>
+      </c>
+      <c r="AL133" s="15">
+        <v>187.07</v>
+      </c>
+    </row>
+    <row r="134" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C134">
+        <v>256219729</v>
+      </c>
+      <c r="D134">
+        <v>364159532</v>
+      </c>
+      <c r="E134">
+        <v>308347347</v>
+      </c>
+      <c r="F134">
+        <v>316257117</v>
+      </c>
+      <c r="G134">
+        <v>10740466</v>
+      </c>
+      <c r="H134">
+        <v>14917567</v>
+      </c>
+      <c r="I134">
+        <v>29674758</v>
+      </c>
+      <c r="J134">
+        <v>15652901</v>
+      </c>
+      <c r="K134">
+        <v>10465937</v>
+      </c>
+      <c r="L134">
+        <v>5186964</v>
+      </c>
+      <c r="M134">
+        <v>632129.74699999997</v>
+      </c>
+      <c r="N134">
+        <v>59241</v>
+      </c>
+      <c r="O134">
+        <v>175573</v>
+      </c>
+      <c r="P134">
+        <v>6053908</v>
+      </c>
+      <c r="Q134">
+        <v>2359673</v>
+      </c>
+      <c r="R134">
+        <v>1953557.5209999999</v>
+      </c>
+      <c r="S134">
+        <v>24084.222222222223</v>
+      </c>
+      <c r="T134">
+        <v>1929473.2987777777</v>
+      </c>
+      <c r="U134">
+        <v>1398713</v>
+      </c>
+      <c r="V134">
+        <v>2701637.4790000003</v>
+      </c>
+      <c r="W134">
+        <v>-125207</v>
+      </c>
+      <c r="X134">
+        <v>341964.47900000028</v>
+      </c>
+      <c r="Y134">
+        <v>216758</v>
+      </c>
+      <c r="Z134">
+        <v>65027</v>
+      </c>
+      <c r="AA134">
+        <v>151730</v>
+      </c>
+      <c r="AB134">
+        <v>-2655772.8650000002</v>
+      </c>
+      <c r="AC134">
+        <v>2.04</v>
+      </c>
+      <c r="AD134" s="12">
+        <v>0.11650000000000001</v>
+      </c>
+      <c r="AE134" s="12">
+        <v>4.6100000000000002E-2</v>
+      </c>
+      <c r="AF134" s="12">
+        <v>5.45E-2</v>
+      </c>
+      <c r="AG134" s="12">
+        <v>1.03E-2</v>
+      </c>
+      <c r="AH134" s="12">
+        <v>0.83189999999999997</v>
+      </c>
+      <c r="AI134" s="12">
+        <v>7.5200000000000003E-2</v>
+      </c>
+      <c r="AJ134" s="12">
+        <v>0.04</v>
+      </c>
+      <c r="AK134" s="12">
+        <v>0.25669999999999998</v>
+      </c>
+      <c r="AL134" s="15">
+        <v>198.92</v>
+      </c>
+    </row>
+    <row r="135" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C135">
+        <v>227801522</v>
+      </c>
+      <c r="D135">
+        <v>322551665</v>
+      </c>
+      <c r="E135">
+        <v>246467329</v>
+      </c>
+      <c r="F135">
+        <v>249412866</v>
+      </c>
+      <c r="G135">
+        <v>12379432</v>
+      </c>
+      <c r="H135">
+        <v>18366706</v>
+      </c>
+      <c r="I135">
+        <v>31058873</v>
+      </c>
+      <c r="J135">
+        <v>11609726</v>
+      </c>
+      <c r="K135">
+        <v>7356460</v>
+      </c>
+      <c r="L135">
+        <v>4253266</v>
+      </c>
+      <c r="M135">
+        <v>1108310</v>
+      </c>
+      <c r="N135">
+        <v>179587</v>
+      </c>
+      <c r="O135">
+        <v>143457</v>
+      </c>
+      <c r="P135">
+        <v>5684619</v>
+      </c>
+      <c r="Q135">
+        <v>344765</v>
+      </c>
+      <c r="R135">
+        <v>1642729</v>
+      </c>
+      <c r="S135">
+        <v>315449</v>
+      </c>
+      <c r="T135">
+        <v>1327280</v>
+      </c>
+      <c r="U135">
+        <v>734245</v>
+      </c>
+      <c r="V135">
+        <v>3307645</v>
+      </c>
+      <c r="W135">
+        <v>-123840</v>
+      </c>
+      <c r="X135">
+        <v>2962880</v>
+      </c>
+      <c r="Y135">
+        <v>2839041</v>
+      </c>
+      <c r="Z135">
+        <v>835500</v>
+      </c>
+      <c r="AA135">
+        <v>2003540</v>
+      </c>
+      <c r="AB135">
+        <v>1337740</v>
+      </c>
+      <c r="AC135">
+        <v>21.82</v>
+      </c>
+      <c r="AD135" s="12">
+        <f>12.62/100</f>
+        <v>0.12619999999999998</v>
+      </c>
+      <c r="AE135" s="12">
+        <f>3.96/100</f>
+        <v>3.9599999999999996E-2</v>
+      </c>
+      <c r="AF135" s="12">
+        <f>5.48/100</f>
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="AG135" s="12">
+        <f>13.5/100</f>
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="AH135" s="12">
+        <f>86.76/100</f>
+        <v>0.86760000000000004</v>
+      </c>
+      <c r="AI135" s="12">
+        <f>6.92/100</f>
+        <v>6.9199999999999998E-2</v>
+      </c>
+      <c r="AJ135" s="12">
+        <f>3.97/100</f>
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="AK135" s="12">
+        <f>24.68/100</f>
+        <v>0.24679999999999999</v>
+      </c>
+      <c r="AL135" s="15">
+        <v>169.1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C136">
+        <v>228209790</v>
+      </c>
+      <c r="D136">
+        <v>367215973</v>
+      </c>
+      <c r="E136">
+        <v>304513546</v>
+      </c>
+      <c r="F136">
+        <v>310001252</v>
+      </c>
+      <c r="G136">
+        <v>7840942</v>
+      </c>
+      <c r="H136">
+        <v>23542490</v>
+      </c>
+      <c r="I136">
+        <v>34087399</v>
+      </c>
+      <c r="J136">
+        <v>13173243</v>
+      </c>
+      <c r="K136">
+        <v>8305338</v>
+      </c>
+      <c r="L136">
+        <v>4867905</v>
+      </c>
+      <c r="M136">
+        <v>1122249</v>
+      </c>
+      <c r="N136">
+        <v>271687</v>
+      </c>
+      <c r="O136">
+        <v>405683</v>
+      </c>
+      <c r="P136">
+        <v>6667524</v>
+      </c>
+      <c r="Q136">
+        <v>814224</v>
+      </c>
+      <c r="R136">
+        <v>2156315</v>
+      </c>
+      <c r="S136">
+        <v>280396.88888888888</v>
+      </c>
+      <c r="T136">
+        <v>1875918.111111111</v>
+      </c>
+      <c r="U136">
+        <v>1174149</v>
+      </c>
+      <c r="V136">
+        <v>3337060</v>
+      </c>
+      <c r="W136">
+        <v>737</v>
+      </c>
+      <c r="X136">
+        <v>2522836</v>
+      </c>
+      <c r="Y136">
+        <v>2523572</v>
+      </c>
+      <c r="Z136">
+        <v>1187434</v>
+      </c>
+      <c r="AA136">
+        <v>1336138</v>
+      </c>
+      <c r="AB136">
+        <v>-3331364</v>
+      </c>
+      <c r="AC136">
+        <v>11.35</v>
+      </c>
+      <c r="AD136" s="12">
+        <v>0.12839999999999999</v>
+      </c>
+      <c r="AE136" s="12">
+        <v>5.0599999999999999E-2</v>
+      </c>
+      <c r="AF136" s="12">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="AG136" s="12">
+        <v>8.0100000000000005E-2</v>
+      </c>
+      <c r="AH136" s="12">
+        <v>0.74950000000000006</v>
+      </c>
+      <c r="AI136" s="12">
+        <v>7.0599999999999996E-2</v>
+      </c>
+      <c r="AJ136" s="12">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="AK136" s="12">
+        <v>0.33510000000000001</v>
+      </c>
+      <c r="AL136" s="15">
+        <v>144.79</v>
+      </c>
+    </row>
+    <row r="137" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C137">
+        <v>206864921</v>
+      </c>
+      <c r="D137">
+        <v>290450994</v>
+      </c>
+      <c r="E137">
+        <v>231566509</v>
+      </c>
+      <c r="F137">
+        <v>243996626</v>
+      </c>
+      <c r="G137">
+        <v>9159435</v>
+      </c>
+      <c r="H137">
+        <v>19402576</v>
+      </c>
+      <c r="I137">
+        <v>31556462</v>
+      </c>
+      <c r="J137">
+        <v>11864475</v>
+      </c>
+      <c r="K137">
+        <v>7445256</v>
+      </c>
+      <c r="L137">
+        <v>4419220</v>
+      </c>
+      <c r="M137">
+        <v>893113.08900000004</v>
+      </c>
+      <c r="N137">
+        <v>92627</v>
+      </c>
+      <c r="O137">
+        <v>231080</v>
+      </c>
+      <c r="P137">
+        <v>5636040</v>
+      </c>
+      <c r="Q137">
+        <v>861530</v>
+      </c>
+      <c r="R137">
+        <v>1154907.169</v>
+      </c>
+      <c r="S137">
+        <v>295807.44444444444</v>
+      </c>
+      <c r="T137">
+        <v>859099.7245555555</v>
+      </c>
+      <c r="U137">
+        <v>432697</v>
+      </c>
+      <c r="V137">
+        <v>4048435.8310000002</v>
+      </c>
+      <c r="W137">
+        <v>-524639</v>
+      </c>
+      <c r="X137">
+        <v>3186905.8310000002</v>
+      </c>
+      <c r="Y137">
+        <v>2662267</v>
+      </c>
+      <c r="Z137">
+        <v>792317</v>
+      </c>
+      <c r="AA137">
+        <v>1869950</v>
+      </c>
+      <c r="AB137">
+        <v>1841715.2509999999</v>
+      </c>
+      <c r="AC137">
+        <v>19.28</v>
+      </c>
+      <c r="AD137" s="12">
+        <v>0.1167</v>
+      </c>
+      <c r="AE137" s="12">
+        <v>4.9599999999999998E-2</v>
+      </c>
+      <c r="AF137" s="12">
+        <v>5.6899999999999999E-2</v>
+      </c>
+      <c r="AG137" s="12">
+        <v>6.0100000000000001E-2</v>
+      </c>
+      <c r="AH137" s="12">
+        <v>0.8609</v>
+      </c>
+      <c r="AI137" s="12">
+        <v>7.1199999999999999E-2</v>
+      </c>
+      <c r="AJ137" s="12">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="AK137" s="12">
+        <v>0.26429999999999998</v>
+      </c>
+      <c r="AL137" s="15">
+        <v>162.63999999999999</v>
+      </c>
+    </row>
+    <row r="138" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C138">
+        <v>279575143</v>
+      </c>
+      <c r="D138">
+        <v>526147537.11500001</v>
+      </c>
+      <c r="E138">
+        <v>447327524.74800003</v>
+      </c>
+      <c r="F138">
+        <v>449981426</v>
+      </c>
+      <c r="G138">
+        <v>2500582</v>
+      </c>
+      <c r="H138">
+        <v>15637377</v>
+      </c>
+      <c r="I138">
+        <v>51578511</v>
+      </c>
+      <c r="J138">
+        <v>13317089</v>
+      </c>
+      <c r="K138">
+        <v>8910160</v>
+      </c>
+      <c r="L138">
+        <v>4406929</v>
+      </c>
+      <c r="M138">
+        <v>640838.755</v>
+      </c>
+      <c r="N138">
+        <v>40794</v>
+      </c>
+      <c r="O138">
+        <v>329238</v>
+      </c>
+      <c r="P138">
+        <v>5417800</v>
+      </c>
+      <c r="Q138">
+        <v>1242504</v>
+      </c>
+      <c r="R138">
+        <v>2132447.7579999999</v>
+      </c>
+      <c r="S138">
+        <v>121116.44444444444</v>
+      </c>
+      <c r="T138">
+        <v>2011331.3135555554</v>
+      </c>
+      <c r="U138">
+        <v>957774</v>
+      </c>
+      <c r="V138">
+        <v>2327578.2420000001</v>
+      </c>
+      <c r="W138">
+        <v>4974</v>
+      </c>
+      <c r="X138">
+        <v>1085074.2420000001</v>
+      </c>
+      <c r="Y138">
+        <v>1090048</v>
+      </c>
+      <c r="Z138">
+        <v>327014</v>
+      </c>
+      <c r="AA138">
+        <v>763033</v>
+      </c>
+      <c r="AB138">
+        <v>-1259145.7649999999</v>
+      </c>
+      <c r="AC138">
+        <v>9.76</v>
+      </c>
+      <c r="AD138" s="12">
+        <v>0.1106</v>
+      </c>
+      <c r="AE138" s="12">
+        <v>4.9599999999999998E-2</v>
+      </c>
+      <c r="AF138" s="12">
+        <v>3.8100000000000002E-2</v>
+      </c>
+      <c r="AG138" s="12">
+        <v>3.04E-2</v>
+      </c>
+      <c r="AH138" s="12">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="AI138" s="12">
+        <v>5.4399999999999997E-2</v>
+      </c>
+      <c r="AJ138" s="12">
+        <v>3.9600000000000003E-2</v>
+      </c>
+      <c r="AK138" s="12">
+        <v>0.41320000000000001</v>
+      </c>
+      <c r="AL138" s="15">
+        <v>329.84</v>
+      </c>
+    </row>
+    <row r="139" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C139">
+        <v>172939131.162</v>
+      </c>
+      <c r="D139">
+        <v>246037461.90000001</v>
+      </c>
+      <c r="E139">
+        <v>207894499.83000001</v>
+      </c>
+      <c r="F139">
+        <v>211205711.956</v>
+      </c>
+      <c r="G139">
+        <v>9379441</v>
+      </c>
+      <c r="H139">
+        <v>13581525.414000001</v>
+      </c>
+      <c r="I139">
+        <v>21399621.614999998</v>
+      </c>
+      <c r="J139">
+        <v>8830755.9220000003</v>
+      </c>
+      <c r="K139">
+        <v>5956323.9919999996</v>
+      </c>
+      <c r="L139">
+        <v>2874431.93</v>
+      </c>
+      <c r="M139">
+        <v>579624.80500000005</v>
+      </c>
+      <c r="N139">
+        <v>297090.77399999998</v>
+      </c>
+      <c r="O139">
+        <v>263643.63099999999</v>
+      </c>
+      <c r="P139">
+        <v>4014791.14</v>
+      </c>
+      <c r="Q139">
+        <v>761982.73300000001</v>
+      </c>
+      <c r="R139">
+        <v>1010736.579</v>
+      </c>
+      <c r="S139">
+        <v>183270.99555555556</v>
+      </c>
+      <c r="T139">
+        <v>827465.58344444446</v>
+      </c>
+      <c r="U139">
+        <v>593084.47399999993</v>
+      </c>
+      <c r="V139">
+        <v>2410970.0870000003</v>
+      </c>
+      <c r="W139">
+        <v>421.60500000000002</v>
+      </c>
+      <c r="X139">
+        <v>1648987.3540000003</v>
+      </c>
+      <c r="Y139">
+        <v>1649438.96</v>
+      </c>
+      <c r="Z139">
+        <v>-2</v>
+      </c>
+      <c r="AA139">
+        <v>1192311.2879999999</v>
+      </c>
+      <c r="AB139">
+        <v>1799639.92</v>
+      </c>
+      <c r="AC139">
+        <v>17.61</v>
+      </c>
+      <c r="AD139" s="12">
+        <f>13.01/100</f>
+        <v>0.13009999999999999</v>
+      </c>
+      <c r="AE139" s="12">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="AF139" s="12">
+        <f>5.28/100</f>
+        <v>5.28E-2</v>
+      </c>
+      <c r="AG139" s="12">
+        <f>11.3/100</f>
+        <v>0.113</v>
+      </c>
+      <c r="AH139" s="12">
+        <f>79.68/100</f>
+        <v>0.79680000000000006</v>
+      </c>
+      <c r="AI139" s="12">
+        <f>6.79/100</f>
+        <v>6.7900000000000002E-2</v>
+      </c>
+      <c r="AJ139" s="12">
+        <f>4/100</f>
+        <v>0.04</v>
+      </c>
+      <c r="AK139" s="12">
+        <f>28.27/100</f>
+        <v>0.28270000000000001</v>
+      </c>
+      <c r="AL139" s="15">
+        <v>157.56</v>
+      </c>
+    </row>
+    <row r="140" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C140">
+        <v>212070665</v>
+      </c>
+      <c r="D140">
+        <v>306068535.527502</v>
+      </c>
+      <c r="E140">
+        <v>243796718.98589599</v>
+      </c>
+      <c r="F140">
+        <v>252623116.50514999</v>
+      </c>
+      <c r="G140">
+        <v>11662559</v>
+      </c>
+      <c r="H140">
+        <v>14089980.189719999</v>
+      </c>
+      <c r="I140">
+        <v>27983577.5265112</v>
+      </c>
+      <c r="J140">
+        <v>11316423.952563001</v>
+      </c>
+      <c r="K140">
+        <v>7200370.3385399999</v>
+      </c>
+      <c r="L140">
+        <v>4116053.614023</v>
+      </c>
+      <c r="M140">
+        <v>780034.37474999996</v>
+      </c>
+      <c r="N140">
+        <v>75196.491439999998</v>
+      </c>
+      <c r="O140">
+        <v>302106.44614000001</v>
+      </c>
+      <c r="P140">
+        <v>5273390.9263530001</v>
+      </c>
+      <c r="Q140">
+        <v>2265145.9835719098</v>
+      </c>
+      <c r="R140">
+        <v>1439421.66949081</v>
+      </c>
+      <c r="S140">
+        <v>84742.628797809331</v>
+      </c>
+      <c r="T140">
+        <v>1354679.0406930007</v>
+      </c>
+      <c r="U140">
+        <v>813416.46577000001</v>
+      </c>
+      <c r="V140">
+        <v>3020552.79109219</v>
+      </c>
+      <c r="W140">
+        <v>7276.8516600000003</v>
+      </c>
+      <c r="X140">
+        <v>755406.80752028013</v>
+      </c>
+      <c r="Y140">
+        <v>762683.65918028401</v>
+      </c>
+      <c r="Z140">
+        <v>232454.18864368799</v>
+      </c>
+      <c r="AA140">
+        <v>530229.47053659603</v>
+      </c>
+      <c r="AB140">
+        <v>-361944.56699999998</v>
+      </c>
+      <c r="AC140">
+        <v>7.55</v>
+      </c>
+      <c r="AD140" s="12">
+        <f>11.19/100</f>
+        <v>0.1119</v>
+      </c>
+      <c r="AE140" s="12">
+        <f>4.5/100</f>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="AF140" s="12">
+        <f>4.99/100</f>
+        <v>4.99E-2</v>
+      </c>
+      <c r="AG140" s="12">
+        <f>3.79/100</f>
+        <v>3.7900000000000003E-2</v>
+      </c>
+      <c r="AH140" s="12">
+        <f>83.78/100</f>
+        <v>0.83779999999999999</v>
+      </c>
+      <c r="AI140" s="12">
+        <f>6.93/100</f>
+        <v>6.93E-2</v>
+      </c>
+      <c r="AJ140" s="12">
+        <f>3.99/100</f>
+        <v>3.9900000000000005E-2</v>
+      </c>
+      <c r="AK140" s="12">
+        <f>25.68/100</f>
+        <v>0.25679999999999997</v>
+      </c>
+      <c r="AL140" s="15">
+        <v>198.61</v>
+      </c>
+    </row>
+    <row r="141" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C141">
+        <v>87506215</v>
+      </c>
+      <c r="D141">
+        <v>151674638</v>
+      </c>
+      <c r="E141">
+        <v>122165207</v>
+      </c>
+      <c r="F141">
+        <v>124881561</v>
+      </c>
+      <c r="G141">
+        <v>2523261</v>
+      </c>
+      <c r="H141">
+        <v>10042368</v>
+      </c>
+      <c r="I141">
+        <v>20383153</v>
+      </c>
+      <c r="J141">
+        <v>4141986</v>
+      </c>
+      <c r="K141">
+        <v>1969517</v>
+      </c>
+      <c r="L141">
+        <v>2172469</v>
+      </c>
+      <c r="M141">
+        <v>695476</v>
+      </c>
+      <c r="N141">
+        <v>329887</v>
+      </c>
+      <c r="O141">
+        <v>21024</v>
+      </c>
+      <c r="P141">
+        <v>3218855</v>
+      </c>
+      <c r="Q141">
+        <v>-250781</v>
+      </c>
+      <c r="R141">
+        <v>803441</v>
+      </c>
+      <c r="S141">
+        <v>260417.33333333334</v>
+      </c>
+      <c r="T141">
+        <v>543023.66666666663</v>
+      </c>
+      <c r="U141">
+        <v>319292</v>
+      </c>
+      <c r="V141">
+        <v>2096122</v>
+      </c>
+      <c r="W141">
+        <v>-3145</v>
+      </c>
+      <c r="X141">
+        <v>2346903</v>
+      </c>
+      <c r="Y141">
+        <v>2343756</v>
+      </c>
+      <c r="Z141">
+        <v>703126</v>
+      </c>
+      <c r="AA141">
+        <v>1640630</v>
+      </c>
+      <c r="AB141">
+        <v>1139059</v>
+      </c>
+      <c r="AC141">
+        <v>32.67</v>
+      </c>
+      <c r="AD141" s="13">
+        <v>0.1694</v>
+      </c>
+      <c r="AE141" s="13">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="AF141" s="13">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="AG141" s="13">
+        <v>0.16039999999999999</v>
+      </c>
+      <c r="AH141" s="13">
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="AI141" s="13">
+        <v>5.1299999999999998E-2</v>
+      </c>
+      <c r="AJ141" s="13">
+        <v>0.04</v>
+      </c>
+      <c r="AK141" s="13">
+        <v>0.48649999999999999</v>
+      </c>
+      <c r="AL141" s="16">
+        <v>202.97</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
